--- a/Tests/Homepage/Homepage_Pass.xlsx
+++ b/Tests/Homepage/Homepage_Pass.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HSH009H01/NRF/617/Sequence/MAIN/?preset=PLP_487</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HSH009H01/NRF/617/Sequence/MAIN/?preset=PLP_615</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HSH009H01/NRF/617/Sequence/MAIN/?preset=PLP_375</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HSH009H01/NRF/617/Sequence/MAIN/?preset=PLP_487</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HSH009H01/NRF/617/Sequence/MAIN/?preset=PLP_200</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HSH009H01/NRF/617/Sequence/MAIN/?preset=PLP_375</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6JNC001J89/NRF/059/Sequence/MAIN/?preset=PLP_1250</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HSH009H01/NRF/617/Sequence/MAIN/?preset=PLP_200</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6JNC001J89/NRF/059/Sequence/MAIN/?preset=PLP_1000</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6JNC001J89/NRF/059/Sequence/MAIN/?preset=PLP_1250</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6JNC001J89/NRF/059/Sequence/MAIN/?preset=PLP_615</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6JNC001J89/NRF/059/Sequence/MAIN/?preset=PLP_1000</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6JNC001J89/NRF/059/Sequence/MAIN/?preset=PLP_487</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6JNC001J89/NRF/059/Sequence/MAIN/?preset=PLP_615</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6JNC001J89/NRF/059/Sequence/MAIN/?preset=PLP_375</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6JNC001J89/NRF/059/Sequence/MAIN/?preset=PLP_487</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6JNC001J89/NRF/059/Sequence/MAIN/?preset=PLP_200</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6JNC001J89/NRF/059/Sequence/MAIN/?preset=PLP_375</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HTT015H02/NRF/002/Sequence/MAIN/?preset=PLP_1250</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6JNC001J89/NRF/059/Sequence/MAIN/?preset=PLP_200</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HTT015H02/NRF/002/Sequence/MAIN/?preset=PLP_1000</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HTT015H02/NRF/002/Sequence/MAIN/?preset=PLP_1250</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HTT015H02/NRF/002/Sequence/MAIN/?preset=PLP_615</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HTT015H02/NRF/002/Sequence/MAIN/?preset=PLP_1000</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HTT015H02/NRF/002/Sequence/MAIN/?preset=PLP_487</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HTT015H02/NRF/002/Sequence/MAIN/?preset=PLP_615</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HTT015H02/NRF/002/Sequence/MAIN/?preset=PLP_375</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HTT015H02/NRF/002/Sequence/MAIN/?preset=PLP_487</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HTT015H02/NRF/002/Sequence/MAIN/?preset=PLP_200</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HTT015H02/NRF/002/Sequence/MAIN/?preset=PLP_375</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6SCH004S02/NRF/042/Sequence/MAIN/?preset=PLP_1250</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HTT015H02/NRF/002/Sequence/MAIN/?preset=PLP_200</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6SCH004S02/NRF/042/Sequence/MAIN/?preset=PLP_1000</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6SCH004S02/NRF/042/Sequence/MAIN/?preset=PLP_1250</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6SCH004S02/NRF/042/Sequence/MAIN/?preset=PLP_615</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6SCH004S02/NRF/042/Sequence/MAIN/?preset=PLP_1000</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6SCH004S02/NRF/042/Sequence/MAIN/?preset=PLP_487</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6SCH004S02/NRF/042/Sequence/MAIN/?preset=PLP_615</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6SCH004S02/NRF/042/Sequence/MAIN/?preset=PLP_375</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6SCH004S02/NRF/042/Sequence/MAIN/?preset=PLP_487</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6SCH004S02/NRF/042/Sequence/MAIN/?preset=PLP_200</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6SCH004S02/NRF/042/Sequence/MAIN/?preset=PLP_375</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SHOES_DESKTOP_JP_V3/?preset=4COL_2561</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6SCH004S02/NRF/042/Sequence/MAIN/?preset=PLP_200</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SHOES_DESKTOP_JP_V3/?preset=4COL_1920</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_2561</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SHOES_DESKTOP_JP_V3/?preset=4COL_1440</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_1920</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SHOES_DESKTOP_JP_V3/?preset=4COL_768</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_1440</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HTT015H02/NRF/002/Swatch/Yes/?preset=PLP_SWATCH</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_768</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,307 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_MOBILE/?preset=4COL_0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_2561</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_1920</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_768</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_MOBILE/?preset=4COL_0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_2561</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_1920</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_768</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_MOBILE/?preset=4COL_0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SHOES_DESKTOP_JP_V3/?preset=4COL_2561</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SHOES_DESKTOP_JP_V3/?preset=4COL_1920</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SHOES_DESKTOP_JP_V3/?preset=4COL_1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SHOES_DESKTOP_JP_V3/?preset=4COL_768</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/SP26_HERO_2_SHOWPAGE/?preset=FULL_2561</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/SP26_HERO_2_SHOWPAGE/?preset=FULL_1920</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/SP26_HERO_2_SHOWPAGE/?preset=FULL_1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/SP26_HERO_2_SHOWPAGE/?preset=FULL_768</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/SP26_HERO_2_SHOWPAGE_MOBILE/?preset=FULL_0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HTT015H02/NRF/002/Swatch/Yes/?preset=PLP_SWATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HTT015H02/NRF/261/Swatch/Yes/?preset=PLP_SWATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/asset/9cccc187-d482-454a-bfc9-03679e6213fc/720p/260305_HP_VIDEO_1_DESKTOP.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/asset/4b7bd987-505c-4e92-9597-0fc8b26d8511/480p/260305_HP_VIDEO_1_MOBILE.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/asset/2aee6795-8fd4-4516-8255-dcbd05a0cc8f/720p/260305_HP_VIDEO_7_DESKTOP.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/asset/15668ea9-68f6-49b1-ad8a-ce7a475fa89d/480p/260305_HP_VIDEO_7_MOBILE.mp4</t>
         </is>
       </c>
     </row>
